--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/MISSOURI_2013.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/MISSOURI_2013.xlsx
@@ -2706,7 +2706,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C131">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C153">
@@ -9132,7 +9132,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C488">
@@ -10194,7 +10194,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C547">
@@ -13650,7 +13650,7 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C739">
